--- a/Item Data.xlsx
+++ b/Item Data.xlsx
@@ -2,18 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abena\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abena\OneDrive\Desktop\Abenadi\Game Projects\Great-Wilderness\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F71D355E-43D3-4557-AEA5-3B41FDA69CAF}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B00534C6-EC5E-43A3-BC26-95BD984D2D94}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9648" xr2:uid="{3A0F34DA-83A3-4355-93D2-1869DD10323B}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="17256" windowHeight="6096" tabRatio="747" activeTab="1" xr2:uid="{EB055037-95A4-419D-B5BA-8DCFC38A869A}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="MATERIAL DATA" sheetId="8" r:id="rId1"/>
+    <sheet name="INDEX" sheetId="9" r:id="rId2"/>
+    <sheet name="WEAPON" sheetId="1" r:id="rId3"/>
+    <sheet name="EQUIPMENT" sheetId="2" r:id="rId4"/>
+    <sheet name="CONSUMABLE" sheetId="3" r:id="rId5"/>
+    <sheet name="MATERIAL" sheetId="4" r:id="rId6"/>
+    <sheet name="TEXT" sheetId="5" r:id="rId7"/>
+    <sheet name="TOOL" sheetId="6" r:id="rId8"/>
+    <sheet name="MISC" sheetId="7" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,67 +33,226 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="18">
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>rarity</t>
-  </si>
-  <si>
-    <t>description</t>
-  </si>
-  <si>
-    <t>tag</t>
-  </si>
-  <si>
-    <t>power</t>
-  </si>
-  <si>
-    <t>durability</t>
-  </si>
-  <si>
-    <t>value</t>
-  </si>
-  <si>
-    <t>weight</t>
-  </si>
-  <si>
-    <t>Wooden Sword</t>
-  </si>
-  <si>
-    <t>Iron Sword</t>
-  </si>
-  <si>
-    <t>Linen Shirt</t>
-  </si>
-  <si>
-    <t>Linen Pants</t>
-  </si>
-  <si>
-    <t>This is the items's description</t>
-  </si>
-  <si>
-    <t>Sword, Wood, Crude</t>
-  </si>
-  <si>
-    <t>Sword, Iron</t>
-  </si>
-  <si>
-    <t>Chest, Linen</t>
-  </si>
-  <si>
-    <t>Leg, Linen</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="71">
+  <si>
+    <t>Item name</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Quality</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Durablity</t>
+  </si>
+  <si>
+    <t>Power</t>
+  </si>
+  <si>
+    <t>Range</t>
+  </si>
+  <si>
+    <t>Weight</t>
+  </si>
+  <si>
+    <t>Axe</t>
+  </si>
+  <si>
+    <t>Material</t>
+  </si>
+  <si>
+    <t>Uncommon</t>
+  </si>
+  <si>
+    <t>Common</t>
+  </si>
+  <si>
+    <t>Iron</t>
+  </si>
+  <si>
+    <t>Sword</t>
+  </si>
+  <si>
+    <t>Rare</t>
+  </si>
+  <si>
+    <t>Black Iron</t>
+  </si>
+  <si>
+    <t>Dragon Bone</t>
+  </si>
+  <si>
+    <t>Wooden axe</t>
+  </si>
+  <si>
+    <t>Wooden sword</t>
+  </si>
+  <si>
+    <t>Wooden hammer</t>
+  </si>
+  <si>
+    <t>Wooden knife</t>
+  </si>
+  <si>
+    <t>Knife</t>
+  </si>
+  <si>
+    <t>Blunt</t>
+  </si>
+  <si>
+    <t>Wooden Spear</t>
+  </si>
+  <si>
+    <t>Spear</t>
+  </si>
+  <si>
+    <t>Wooden Bow</t>
+  </si>
+  <si>
+    <t>Bow</t>
+  </si>
+  <si>
+    <t>Hammer</t>
+  </si>
+  <si>
+    <t>Makeshift Club</t>
+  </si>
+  <si>
+    <t>Bronze knuckles</t>
+  </si>
+  <si>
+    <t>Panabas blade</t>
+  </si>
+  <si>
+    <t>Wooden pole</t>
+  </si>
+  <si>
+    <t>Pole</t>
+  </si>
+  <si>
+    <t>Blade</t>
+  </si>
+  <si>
+    <t>Hand</t>
+  </si>
+  <si>
+    <t>Iron Star</t>
+  </si>
+  <si>
+    <t>Throwable</t>
+  </si>
+  <si>
+    <t>Special</t>
+  </si>
+  <si>
+    <t>Lion Jade Seal</t>
+  </si>
+  <si>
+    <t>Bronze Hand Bell</t>
+  </si>
+  <si>
+    <t>Meters</t>
+  </si>
+  <si>
+    <t>Kilogram</t>
+  </si>
+  <si>
+    <t>Wood</t>
+  </si>
+  <si>
+    <t>Bronze</t>
+  </si>
+  <si>
+    <t>Refined Bronze</t>
+  </si>
+  <si>
+    <t>Jade</t>
+  </si>
+  <si>
+    <t>Soldier Iron Spear</t>
+  </si>
+  <si>
+    <t>Iron Short Sword</t>
+  </si>
+  <si>
+    <t>Jade Short Sword</t>
+  </si>
+  <si>
+    <t>Green Iron Short Sword</t>
+  </si>
+  <si>
+    <t>Tempered Iron</t>
+  </si>
+  <si>
+    <t>Refined</t>
+  </si>
+  <si>
+    <t>Tempered</t>
+  </si>
+  <si>
+    <t>Crude</t>
+  </si>
+  <si>
+    <t>Rusty</t>
+  </si>
+  <si>
+    <t>Gold</t>
+  </si>
+  <si>
+    <t>Gold Bronze</t>
+  </si>
+  <si>
+    <t>Millennium Iron</t>
+  </si>
+  <si>
+    <t>Meteorite Iron</t>
+  </si>
+  <si>
+    <t>Defense</t>
+  </si>
+  <si>
+    <t>Part</t>
+  </si>
+  <si>
+    <t>Energy</t>
+  </si>
+  <si>
+    <t>Effect</t>
+  </si>
+  <si>
+    <t>Heavier weapons slows down attack speed</t>
+  </si>
+  <si>
+    <t>Slash</t>
+  </si>
+  <si>
+    <t>Piercing</t>
+  </si>
+  <si>
+    <t>Ignores part of the defense</t>
+  </si>
+  <si>
+    <t>Can cause bleeding against target with no armor or defense</t>
+  </si>
+  <si>
+    <t>Higher crit damage. Armor Penetration by percentage</t>
+  </si>
+  <si>
+    <t>Sound</t>
+  </si>
+  <si>
+    <t>Attack Types</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -95,7 +262,23 @@
     </font>
     <font>
       <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -110,7 +293,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -118,24 +301,331 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="49">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFAC75D5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFAC75D5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFAC75D5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFAC75D5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFAC75D5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="4" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFAC75D5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFF6D6D"/>
+      <color rgb="FFAC75D5"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -145,6 +635,67 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3FC7D7B4-7626-48B0-9065-EEAD088E9102}" name="Table1" displayName="Table1" ref="A3:I20" totalsRowShown="0" headerRowDxfId="48" dataDxfId="47">
+  <autoFilter ref="A3:I20" xr:uid="{B47E3D63-937D-4B63-A1E2-9120F80BF138}"/>
+  <sortState ref="A4:I20">
+    <sortCondition descending="1" ref="C3:C20"/>
+  </sortState>
+  <tableColumns count="9">
+    <tableColumn id="1" xr3:uid="{5182B3AF-16C0-4765-8D21-D8366E99810B}" name="Item name" dataDxfId="46"/>
+    <tableColumn id="2" xr3:uid="{A328B9F0-A359-4785-88CB-58AD3403335F}" name="Quality" dataDxfId="45"/>
+    <tableColumn id="3" xr3:uid="{0BC7CBBB-8E37-48B5-92B7-BD70F73815BF}" name="Category" dataDxfId="44"/>
+    <tableColumn id="4" xr3:uid="{039B475B-7A93-4A92-AFB2-627A5BD61094}" name="Value" dataDxfId="43"/>
+    <tableColumn id="5" xr3:uid="{98157800-151E-49DA-BACB-714F37330C1E}" name="Durablity" dataDxfId="42"/>
+    <tableColumn id="6" xr3:uid="{F9193B54-A8D6-4BDC-955D-52C96EF208B2}" name="Power" dataDxfId="41"/>
+    <tableColumn id="7" xr3:uid="{803D2091-C4B6-4603-BC37-9210EBC95002}" name="Range" dataDxfId="40"/>
+    <tableColumn id="8" xr3:uid="{1C130944-E743-4BFB-A51F-EDBBA43BADDA}" name="Weight" dataDxfId="39"/>
+    <tableColumn id="9" xr3:uid="{FB14FE84-D1E1-4028-8156-9AA11AED8A4B}" name="Material" dataDxfId="38"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{763AE351-85DB-4A70-9003-7F1C96DA6A20}" name="Table15" displayName="Table15" ref="A3:I4" insertRow="1" totalsRowShown="0" headerRowDxfId="37" dataDxfId="36">
+  <autoFilter ref="A3:I4" xr:uid="{528D5FF5-B3B3-4138-A51C-7D520F76C8C8}"/>
+  <sortState ref="A4:I4">
+    <sortCondition descending="1" ref="C3:C4"/>
+  </sortState>
+  <tableColumns count="9">
+    <tableColumn id="1" xr3:uid="{8E3DB150-957D-48D7-AAF8-937DC8C8002F}" name="Item name" dataDxfId="35"/>
+    <tableColumn id="2" xr3:uid="{D9220CFC-7E92-4E23-9A49-622F6FE0B17E}" name="Quality" dataDxfId="34"/>
+    <tableColumn id="3" xr3:uid="{5EDA9625-A26E-41A5-93D0-D8750CCEA93A}" name="Category" dataDxfId="33"/>
+    <tableColumn id="7" xr3:uid="{5E2A23C2-AABA-4407-9EBC-62D4531C0772}" name="Part" dataDxfId="27"/>
+    <tableColumn id="4" xr3:uid="{B0169C65-00DA-4CCE-9180-EB7D172F7762}" name="Value" dataDxfId="32"/>
+    <tableColumn id="5" xr3:uid="{5ED7678F-AC88-4247-9BC6-BC61B3996818}" name="Durablity" dataDxfId="31"/>
+    <tableColumn id="6" xr3:uid="{9DB31BED-003F-410F-ABB4-2642A76998A6}" name="Defense" dataDxfId="30"/>
+    <tableColumn id="8" xr3:uid="{11BEC19A-7E9B-44FF-8BA9-8394D10D84C7}" name="Weight" dataDxfId="29"/>
+    <tableColumn id="9" xr3:uid="{EF061F1A-1A95-404D-94AF-4D861647974C}" name="Material" dataDxfId="28"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{83704FEB-1DDC-4CAC-B0DD-AA2885265D8E}" name="Table156" displayName="Table156" ref="A2:G3" insertRow="1" totalsRowShown="0" headerRowDxfId="26" dataDxfId="25">
+  <autoFilter ref="A2:G3" xr:uid="{B28467A0-F890-4FEF-87E8-798D0F7615A0}"/>
+  <sortState ref="A3:G3">
+    <sortCondition descending="1" ref="C3:C4"/>
+  </sortState>
+  <tableColumns count="7">
+    <tableColumn id="1" xr3:uid="{23D03192-6454-4CEF-B7CE-0FAF07349979}" name="Item name" dataDxfId="24"/>
+    <tableColumn id="2" xr3:uid="{6BF7B678-09E0-4ACE-AE63-AD7F02F455D1}" name="Quality" dataDxfId="23"/>
+    <tableColumn id="3" xr3:uid="{1DA43B20-19B8-48E0-ABC5-5A6517CD4BD3}" name="Category" dataDxfId="22"/>
+    <tableColumn id="4" xr3:uid="{226656FA-1412-4B8E-AA93-ECBD01F62A3C}" name="Value" dataDxfId="21"/>
+    <tableColumn id="5" xr3:uid="{FC402AFC-1188-4556-88D1-DAC690A6BFCF}" name="Energy" dataDxfId="20"/>
+    <tableColumn id="6" xr3:uid="{E70AD0CE-A9B5-4494-943A-4E01CF039341}" name="Effect" dataDxfId="19"/>
+    <tableColumn id="8" xr3:uid="{3110B0FC-8A41-4CEB-BEC8-E1A65917CC20}" name="Weight" dataDxfId="18"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -443,196 +994,1078 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8358AA9A-A867-4E65-AF16-896FC93C15AB}">
-  <dimension ref="A1:I12"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C9CBBA9-6D63-405E-A819-44A9FDDBFABB}">
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="B2:E11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="8.88671875" style="2"/>
-    <col min="2" max="2" width="14.33203125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="11" style="2" customWidth="1"/>
-    <col min="4" max="4" width="30.44140625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="28.109375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="8.5546875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="9.6640625" style="2" customWidth="1"/>
-    <col min="8" max="16384" width="8.88671875" style="2"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
-        <v>1001</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="2">
-        <v>1</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A3" s="2">
-        <v>1002</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="2">
-        <v>1</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="2" t="s">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
+        <v>52</v>
+      </c>
+      <c r="E5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="E6" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
-        <v>1003</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="2">
-        <v>1</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="2" t="s">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="E7" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="2">
-        <v>1004</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="2">
-        <v>1</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="2">
-        <v>1005</v>
-      </c>
-      <c r="C6" s="2">
-        <v>1</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="2">
-        <v>1006</v>
-      </c>
-      <c r="C7" s="2">
-        <v>1</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="2">
-        <v>1007</v>
-      </c>
-      <c r="C8" s="2">
-        <v>1</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="2">
-        <v>1008</v>
-      </c>
-      <c r="C9" s="2">
-        <v>1</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="2">
-        <v>1009</v>
-      </c>
-      <c r="C10" s="2">
-        <v>1</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="2">
-        <v>1010</v>
-      </c>
-      <c r="C11" s="2">
-        <v>1</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="2">
-        <v>1011</v>
-      </c>
-      <c r="C12" s="2">
-        <v>1</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>13</v>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="E8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="E9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="E10" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="E11" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1307F494-343A-490F-8A02-57404B9E65EF}">
+  <sheetPr codeName="Sheet2"/>
+  <dimension ref="D7:J19"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="7" spans="4:10" ht="18" x14ac:dyDescent="0.35">
+      <c r="D7" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
+      <c r="G7" s="10"/>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10"/>
+      <c r="J7" s="10"/>
+    </row>
+    <row r="9" spans="4:10" x14ac:dyDescent="0.3">
+      <c r="D9" s="9" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="F9" s="8"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+    </row>
+    <row r="10" spans="4:10" x14ac:dyDescent="0.3">
+      <c r="D10" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+    </row>
+    <row r="11" spans="4:10" x14ac:dyDescent="0.3">
+      <c r="D11" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+    </row>
+    <row r="12" spans="4:10" x14ac:dyDescent="0.3">
+      <c r="D12" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="E12" s="1"/>
+    </row>
+    <row r="13" spans="4:10" x14ac:dyDescent="0.3">
+      <c r="D13" s="9" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="19" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D19" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="E10:J10"/>
+    <mergeCell ref="E11:J11"/>
+    <mergeCell ref="E9:J9"/>
+    <mergeCell ref="D7:J7"/>
+  </mergeCells>
+  <conditionalFormatting sqref="D9:D13">
+    <cfRule type="cellIs" dxfId="17" priority="5" operator="equal">
+      <formula>"Epic"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="16" priority="7" operator="equal">
+      <formula>"Uncommon"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="8" operator="equal">
+      <formula>"Common"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D9:D13">
+    <cfRule type="cellIs" dxfId="15" priority="6" operator="equal">
+      <formula>"Rare"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D19">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+      <formula>"Epic"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+      <formula>"Uncommon"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="equal">
+      <formula>"Common"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D19">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+      <formula>"Rare"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{232F131A-87DA-416A-9278-D28D17715E60}">
+  <sheetPr codeName="Sheet3"/>
+  <dimension ref="A2:I20"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="28.21875" style="3" customWidth="1"/>
+    <col min="2" max="2" width="15.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="13.21875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="15.33203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="15.6640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="13.109375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="15.109375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="20.109375" style="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="G2" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" s="1">
+        <v>15</v>
+      </c>
+      <c r="E4" s="1">
+        <v>20</v>
+      </c>
+      <c r="F4" s="1">
+        <v>1</v>
+      </c>
+      <c r="G4" s="1">
+        <v>30</v>
+      </c>
+      <c r="H4" s="1">
+        <v>0.1</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="1">
+        <v>10</v>
+      </c>
+      <c r="E5" s="1">
+        <v>10</v>
+      </c>
+      <c r="F5" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="G5" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="H5" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="1">
+        <v>45</v>
+      </c>
+      <c r="E6" s="1">
+        <v>28</v>
+      </c>
+      <c r="F6" s="1">
+        <v>2</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="1">
+        <v>400</v>
+      </c>
+      <c r="E7" s="1">
+        <v>50</v>
+      </c>
+      <c r="F7" s="1">
+        <v>4</v>
+      </c>
+      <c r="G7" s="1">
+        <v>1.3</v>
+      </c>
+      <c r="H7" s="1">
+        <v>2</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="1">
+        <v>50</v>
+      </c>
+      <c r="E8" s="1">
+        <v>30</v>
+      </c>
+      <c r="F8" s="1">
+        <v>2</v>
+      </c>
+      <c r="G8" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="H8" s="1">
+        <v>1.6</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="1">
+        <v>210</v>
+      </c>
+      <c r="E9" s="1">
+        <v>40</v>
+      </c>
+      <c r="F9" s="1">
+        <v>5</v>
+      </c>
+      <c r="G9" s="1">
+        <v>30</v>
+      </c>
+      <c r="H9" s="1">
+        <v>0.9</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="1">
+        <v>755</v>
+      </c>
+      <c r="E10" s="1">
+        <v>110</v>
+      </c>
+      <c r="F10" s="1">
+        <v>15</v>
+      </c>
+      <c r="G10" s="1">
+        <v>50</v>
+      </c>
+      <c r="H10" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" s="1">
+        <v>10</v>
+      </c>
+      <c r="E11" s="1">
+        <v>10</v>
+      </c>
+      <c r="F11" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="G11" s="1">
+        <v>3</v>
+      </c>
+      <c r="H11" s="1">
+        <v>1</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" s="1">
+        <v>50</v>
+      </c>
+      <c r="E12" s="1">
+        <v>30</v>
+      </c>
+      <c r="F12" s="1">
+        <v>1.9</v>
+      </c>
+      <c r="G12" s="1">
+        <v>3</v>
+      </c>
+      <c r="H12" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" s="1">
+        <v>10</v>
+      </c>
+      <c r="E13" s="1">
+        <v>10</v>
+      </c>
+      <c r="F13" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="G13" s="1">
+        <v>3</v>
+      </c>
+      <c r="H13" s="1">
+        <v>1</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D14" s="1">
+        <v>8</v>
+      </c>
+      <c r="E14" s="1">
+        <v>5</v>
+      </c>
+      <c r="F14" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="G14" s="1">
+        <v>1</v>
+      </c>
+      <c r="H14" s="1">
+        <v>0.3</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D15" s="1">
+        <v>20</v>
+      </c>
+      <c r="E15" s="1">
+        <v>25</v>
+      </c>
+      <c r="F15" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="G15" s="1">
+        <v>1</v>
+      </c>
+      <c r="H15" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D16" s="1">
+        <v>10</v>
+      </c>
+      <c r="E16" s="1">
+        <v>10</v>
+      </c>
+      <c r="F16" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="G16" s="1">
+        <v>2.8</v>
+      </c>
+      <c r="H16" s="1">
+        <v>2.5</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D17" s="1">
+        <v>10</v>
+      </c>
+      <c r="E17" s="1">
+        <v>8</v>
+      </c>
+      <c r="F17" s="1">
+        <v>0.4</v>
+      </c>
+      <c r="G17" s="1">
+        <v>100</v>
+      </c>
+      <c r="H17" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="D18" s="1">
+        <v>12</v>
+      </c>
+      <c r="E18" s="1">
+        <v>15</v>
+      </c>
+      <c r="F18" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="G18" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="H18" s="1">
+        <v>1.3</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D19" s="1">
+        <v>35</v>
+      </c>
+      <c r="E19" s="1">
+        <v>23</v>
+      </c>
+      <c r="F19" s="1">
+        <v>2</v>
+      </c>
+      <c r="G19" s="1">
+        <v>1.5</v>
+      </c>
+      <c r="H19" s="1">
+        <v>1</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="1">
+        <v>10</v>
+      </c>
+      <c r="E20" s="1">
+        <v>10</v>
+      </c>
+      <c r="F20" s="1">
+        <v>0.2</v>
+      </c>
+      <c r="G20" s="1">
+        <v>1.3</v>
+      </c>
+      <c r="H20" s="1">
+        <v>0.9</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="D1:D1048576">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color theme="0"/>
+        <color rgb="FFFF6D6D"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E1:E1048576">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color theme="0"/>
+        <color rgb="FFFF6D6D"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F1:F1048576">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color theme="0"/>
+        <color rgb="FFFF6D6D"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B16:B17 B1:B13 B19:B28 B33:B1048576">
+    <cfRule type="cellIs" dxfId="14" priority="5" operator="equal">
+      <formula>"Epic"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="13" priority="7" operator="equal">
+      <formula>"Uncommon"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="8" operator="equal">
+      <formula>"Common"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B16:B17 B1:B13 B19:B28 B33:B1048576">
+    <cfRule type="cellIs" dxfId="12" priority="6" operator="equal">
+      <formula>"Rare"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B15">
+    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
+      <formula>"Epic"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="10" priority="3" operator="equal">
+      <formula>"Uncommon"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="equal">
+      <formula>"Common"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B15">
+    <cfRule type="cellIs" dxfId="9" priority="2" operator="equal">
+      <formula>"Rare"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BE29D4A-062F-4388-920D-736CB8985E68}">
+  <sheetPr codeName="Sheet4"/>
+  <dimension ref="A3:I4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="20.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.6640625" customWidth="1"/>
+    <col min="3" max="4" width="16.5546875" customWidth="1"/>
+    <col min="5" max="5" width="14.21875" customWidth="1"/>
+    <col min="6" max="6" width="17.77734375" customWidth="1"/>
+    <col min="7" max="7" width="14.109375" customWidth="1"/>
+    <col min="8" max="8" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="3"/>
+      <c r="B4" s="1"/>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B3:B4">
+    <cfRule type="cellIs" dxfId="8" priority="5" operator="equal">
+      <formula>"Epic"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="7" priority="7" operator="equal">
+      <formula>"Uncommon"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="8" operator="equal">
+      <formula>"Common"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B3:B4">
+    <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
+      <formula>"Rare"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E3:E4">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color theme="0"/>
+        <color rgb="FFFF6D6D"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F3:F4">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color theme="0"/>
+        <color rgb="FFFF6D6D"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G3:G4">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color theme="0"/>
+        <color rgb="FFFF6D6D"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E14D498-82F0-4DA1-9C57-02DBF003CEEC}">
+  <sheetPr codeName="Sheet5"/>
+  <dimension ref="A2:G3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.21875" customWidth="1"/>
+    <col min="2" max="2" width="13" customWidth="1"/>
+    <col min="3" max="3" width="15.21875" customWidth="1"/>
+    <col min="4" max="4" width="13.44140625" customWidth="1"/>
+    <col min="5" max="5" width="15" customWidth="1"/>
+    <col min="6" max="6" width="13.44140625" customWidth="1"/>
+    <col min="7" max="7" width="15.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="3"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="B2:B3">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
+      <formula>"Epic"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="3" operator="equal">
+      <formula>"Uncommon"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="equal">
+      <formula>"Common"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2:B3">
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
+      <formula>"Rare"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D2:D3">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color theme="0"/>
+        <color rgb="FFFF6D6D"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E3">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color theme="0"/>
+        <color rgb="FFFF6D6D"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F3">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color theme="0"/>
+        <color rgb="FFFF6D6D"/>
+        <color rgb="FFFF0000"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD9789C5-1EC5-46C5-8FF6-17DEF2326735}">
+  <sheetPr codeName="Sheet6"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1D23805-450E-4F1C-82E1-81D47C2850F1}">
+  <sheetPr codeName="Sheet7"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6114DF4F-9E77-40BB-882E-B30647137D8B}">
+  <sheetPr codeName="Sheet8"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC2BEA7F-3584-4C6D-A848-FE539D182DF5}">
+  <sheetPr codeName="Sheet9"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>